--- a/Data/True_data/prior_data/income_statement.xlsx
+++ b/Data/True_data/prior_data/income_statement.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1434.12</v>
+        <v>1258.59</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>582.55</v>
+        <v>576.8099999999999</v>
       </c>
     </row>
     <row r="8">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>851.5700000000001</v>
+        <v>681.78</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>314.91</v>
+        <v>336.02</v>
       </c>
     </row>
     <row r="10">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>144.61</v>
+        <v>84.63</v>
       </c>
     </row>
     <row r="11">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>55.37</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="12">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>514.89</v>
+        <v>453.41</v>
       </c>
     </row>
     <row r="13">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>336.68</v>
+        <v>228.36</v>
       </c>
     </row>
     <row r="14">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>18.35</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="15">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>-2.33</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>316</v>
+        <v>205.88</v>
       </c>
     </row>
     <row r="17">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>67.28</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="18">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>248.72</v>
+        <v>149.69</v>
       </c>
     </row>
   </sheetData>
